--- a/EIIS_Final_Products_04192026.xlsx
+++ b/EIIS_Final_Products_04192026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soharr\Desktop\GWU\Praxis Chapters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soharr\Desktop\GWU\Summer 2026\Session 5\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE14DE6-817B-4B0C-BC84-1D209E17ADCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53CF71C-E4C8-48B7-A48E-F8E495A82A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2145" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -2658,21 +2658,46 @@
     <xf numFmtId="164" fontId="37" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2692,42 +2717,17 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3129,7 +3129,7 @@
   <sheetData>
     <row r="1" spans="2:10" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="108" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="106"/>
@@ -3142,7 +3142,7 @@
       <c r="J2" s="106"/>
     </row>
     <row r="3" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="109" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="106"/>
@@ -3155,7 +3155,7 @@
       <c r="J3" s="106"/>
     </row>
     <row r="4" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="120"/>
+      <c r="B4" s="119"/>
       <c r="C4" s="106"/>
       <c r="D4" s="106"/>
       <c r="E4" s="106"/>
@@ -3169,21 +3169,21 @@
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="107" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="112" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="108"/>
+      <c r="C6" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="112"/>
+      <c r="E6" s="131" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="105"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="106"/>
       <c r="D7" s="106"/>
       <c r="E7" s="106"/>
@@ -3197,21 +3197,21 @@
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="122" t="s">
+      <c r="C8" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="126" t="s">
+      <c r="D8" s="112"/>
+      <c r="E8" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="108"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="112"/>
     </row>
     <row r="9" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="105"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="106"/>
       <c r="D9" s="106"/>
       <c r="E9" s="106"/>
@@ -3225,21 +3225,21 @@
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="108"/>
-      <c r="E10" s="109" t="s">
+      <c r="D10" s="112"/>
+      <c r="E10" s="129" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="108"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="112"/>
     </row>
     <row r="11" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="105"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="106"/>
       <c r="D11" s="106"/>
       <c r="E11" s="106"/>
@@ -3253,21 +3253,21 @@
       <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="125" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="108"/>
-      <c r="E12" s="121" t="s">
+      <c r="D12" s="112"/>
+      <c r="E12" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="108"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="112"/>
     </row>
     <row r="13" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="105"/>
+      <c r="B13" s="117"/>
       <c r="C13" s="106"/>
       <c r="D13" s="106"/>
       <c r="E13" s="106"/>
@@ -3281,21 +3281,21 @@
       <c r="B14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="111" t="s">
+      <c r="C14" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="108"/>
-      <c r="E14" s="125" t="s">
+      <c r="D14" s="112"/>
+      <c r="E14" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="108"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="112"/>
     </row>
     <row r="15" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="105"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="106"/>
       <c r="D15" s="106"/>
       <c r="E15" s="106"/>
@@ -3309,21 +3309,21 @@
       <c r="B16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="108"/>
-      <c r="E16" s="117" t="s">
+      <c r="D16" s="112"/>
+      <c r="E16" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="110"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="108"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="112"/>
     </row>
     <row r="17" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="105"/>
+      <c r="B17" s="117"/>
       <c r="C17" s="106"/>
       <c r="D17" s="106"/>
       <c r="E17" s="106"/>
@@ -3337,21 +3337,21 @@
       <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="127" t="s">
+      <c r="C18" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="108"/>
-      <c r="E18" s="118" t="s">
+      <c r="D18" s="112"/>
+      <c r="E18" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="108"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="112"/>
     </row>
     <row r="19" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="105"/>
+      <c r="B19" s="117"/>
       <c r="C19" s="106"/>
       <c r="D19" s="106"/>
       <c r="E19" s="106"/>
@@ -3365,21 +3365,21 @@
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="128" t="s">
+      <c r="D20" s="112"/>
+      <c r="E20" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="108"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="112"/>
     </row>
     <row r="21" spans="2:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="105"/>
+      <c r="B21" s="117"/>
       <c r="C21" s="106"/>
       <c r="D21" s="106"/>
       <c r="E21" s="106"/>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="24" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="114" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="106"/>
@@ -3404,7 +3404,7 @@
       <c r="J25" s="106"/>
     </row>
     <row r="26" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="119" t="s">
+      <c r="B26" s="118" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="106"/>
@@ -3417,7 +3417,7 @@
       <c r="J26" s="106"/>
     </row>
     <row r="27" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="123" t="str">
+      <c r="B27" s="114" t="str">
         <f>CONCATENATE("H3 SUPPORTED ★ — RM→IS: β=",TEXT('SEM Weights'!$C$9,"0.000"),", p&lt;0.001  |  RM is STRONGEST predictor  |  ARS = P × I × ",TEXT('SEM Weights'!$C$9,"0.000"))</f>
         <v>H3 SUPPORTED ★ — RM→IS: β=0.380, p&lt;0.001  |  RM is STRONGEST predictor  |  ARS = P × I × 0.380</v>
       </c>
@@ -3432,6 +3432,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E16:J16"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="E14:J14"/>
@@ -3448,20 +3462,6 @@
     <mergeCell ref="B25:J25"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="B19:J19"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="E18:J18"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="E6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3486,7 +3486,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="106"/>
@@ -3500,7 +3500,7 @@
       <c r="J2" s="106"/>
     </row>
     <row r="3" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="106"/>
@@ -3514,18 +3514,18 @@
       <c r="J3" s="106"/>
     </row>
     <row r="6" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="108"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
     </row>
     <row r="7" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -3640,13 +3640,13 @@
       <c r="J10" s="17"/>
     </row>
     <row r="14" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="108"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
     </row>
     <row r="15" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
@@ -3819,16 +3819,16 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="122" t="s">
+      <c r="A28" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="108"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="112"/>
     </row>
     <row r="29" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
@@ -3934,15 +3934,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="122" t="s">
+      <c r="A38" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="110"/>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="108"/>
+      <c r="B38" s="111"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="112"/>
     </row>
     <row r="39" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
@@ -4062,14 +4062,14 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="122" t="s">
+      <c r="A48" s="121" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="110"/>
-      <c r="C48" s="110"/>
-      <c r="D48" s="110"/>
-      <c r="E48" s="110"/>
-      <c r="F48" s="108"/>
+      <c r="B48" s="111"/>
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="111"/>
+      <c r="F48" s="112"/>
     </row>
     <row r="49" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
@@ -4183,7 +4183,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>116</v>
       </c>
       <c r="B2" s="106"/>
@@ -4747,7 +4747,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:12" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>143</v>
       </c>
       <c r="B2" s="106"/>
@@ -4763,7 +4763,7 @@
       <c r="L2" s="106"/>
     </row>
     <row r="3" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>144</v>
       </c>
       <c r="B3" s="106"/>
@@ -12947,7 +12947,7 @@
         <v>0.76</v>
       </c>
       <c r="I200" s="71" t="str">
-        <f t="shared" ref="I200:I231" si="12">IF(H200&gt;12,"Critical",IF(H200&gt;=6,"High",IF(H200&gt;=3,"Moderate","Low")))</f>
+        <f t="shared" ref="I200:I204" si="12">IF(H200&gt;12,"Critical",IF(H200&gt;=6,"High",IF(H200&gt;=3,"Moderate","Low")))</f>
         <v>Low</v>
       </c>
       <c r="J200" s="66" t="s">
@@ -13151,7 +13151,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>551</v>
       </c>
       <c r="B2" s="106"/>
@@ -13164,7 +13164,7 @@
       <c r="I2" s="106"/>
     </row>
     <row r="3" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>552</v>
       </c>
       <c r="B3" s="106"/>
@@ -13180,12 +13180,12 @@
       <c r="B6" s="134" t="s">
         <v>553</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="108"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112"/>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="72" t="s">
@@ -13388,7 +13388,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>565</v>
       </c>
       <c r="B2" s="106"/>
@@ -13406,7 +13406,7 @@
       <c r="N2" s="106"/>
     </row>
     <row r="3" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>566</v>
       </c>
       <c r="B3" s="106"/>
@@ -14902,7 +14902,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>591</v>
       </c>
       <c r="B2" s="106"/>
@@ -14914,7 +14914,7 @@
       <c r="H2" s="106"/>
     </row>
     <row r="3" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>592</v>
       </c>
       <c r="B3" s="106"/>
@@ -15107,7 +15107,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="107" t="s">
         <v>595</v>
       </c>
       <c r="B2" s="106"/>
@@ -15118,7 +15118,7 @@
       <c r="G2" s="106"/>
     </row>
     <row r="3" spans="1:7" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="105" t="s">
         <v>596</v>
       </c>
       <c r="B3" s="106"/>
